--- a/Archivos_Compartidos/Cursos RH/Cultura/202510 Examen Cultura cRespuestas.xlsx
+++ b/Archivos_Compartidos/Cursos RH/Cultura/202510 Examen Cultura cRespuestas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://santandernet-my.sharepoint.com/personal/n844756_corp_santanderam_com/Documents/Documentos/+ Riesgos/01.1 Temas relevantes (2)/95. Capacitación anual regulatoria/2025/2. Cultura/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://santandernet-my.sharepoint.com/personal/n854611_corp_santanderam_com/Documents/Documentos/GitHub/SAM_Santander/SAM_Santander/Archivos_Compartidos/Cursos RH/Cultura/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="6" documentId="8_{E568454E-4C88-4692-B75C-974DF9C400AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFFD6CAA-90A4-4DD0-B7EE-48203B0F1383}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12495" yWindow="0" windowWidth="12810" windowHeight="15135" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -159,15 +159,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -604,14 +604,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.36328125" customWidth="1"/>
-    <col min="4" max="4" width="13.90625" customWidth="1"/>
-    <col min="8" max="8" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="8" max="8" width="27.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G2" s="1" t="s">
         <v>0</v>
       </c>
@@ -619,7 +619,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G3" s="1" t="s">
         <v>1</v>
       </c>
@@ -627,24 +627,24 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>3</v>
       </c>
@@ -652,17 +652,17 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>5</v>
       </c>
@@ -670,12 +670,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>3</v>
       </c>
@@ -683,7 +683,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>4</v>
       </c>
@@ -691,32 +691,32 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
@@ -724,7 +724,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>5</v>
       </c>
@@ -732,12 +732,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>3</v>
       </c>
@@ -745,17 +745,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="5" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>5</v>
       </c>
@@ -763,12 +763,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>3</v>
       </c>
@@ -776,7 +776,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>4</v>
       </c>
@@ -784,32 +784,32 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="5" t="s">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B37" s="7" t="b">
+      <c r="B37" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>4</v>
       </c>
@@ -817,7 +817,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>5</v>
       </c>
